--- a/ema-regulation-ai/export/EMA_analysis_results.xlsx
+++ b/ema-regulation-ai/export/EMA_analysis_results.xlsx
@@ -627,7 +627,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Alignment 有下界也有上界：随机解释 = 0.200（各族部署边际率），同特征的监督探针 = 0.904。脱离这两个界读该列没有意义。</t>
+          <t>Alignment 有下界也有上界：随机解释 = 0.200（各族部署边际率），同特征的监督探针 = 0.764。脱离这两个界读该列没有意义。</t>
         </is>
       </c>
     </row>
@@ -670,13 +670,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>参与者数 participants</t>
+          <t>学生数 pupils</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>420</v>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>四至六年级，9–12 岁</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -702,11 +706,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>14 天 × 6 次</t>
+          <t>12 个上学日 × 每天 4 次</t>
         </is>
       </c>
     </row>
@@ -780,7 +784,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>以参与者计</t>
+          <t>以学生计</t>
         </is>
       </c>
     </row>
@@ -845,7 +849,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.7745</v>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
     </row>
@@ -871,12 +875,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.355 (0.146)</t>
+          <t>0.244 (0.185)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>瞬时负性情绪一阶自相关；文献社区样本约 0.35</t>
+          <t>瞬时负性情绪一阶自相关；低于成人社区样本，方向符合发展预期</t>
         </is>
       </c>
     </row>
@@ -888,63 +892,63 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>范围 62–81</t>
+          <t>范围 26–44</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ERQ 重评 M (SD)</t>
+          <t>ERQ-CA 重评 M (SD)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4.89 (0.85)</t>
+          <t>3.62 (0.71)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>已发表值 4.9 (0.9)</t>
+          <t>Gullone &amp; Taffe (2012) 报告条目均值 3.59</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ERQ 抑制 M (SD)</t>
+          <t>ERQ-CA 抑制 M (SD)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3.38 (1.12)</t>
+          <t>2.64 (0.82)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>已发表值 3.4 (1.1)</t>
+          <t>Gullone &amp; Taffe (2012) 报告条目均值 2.64</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DERS 总分 M (SD)</t>
+          <t>ERC 教师报告 M (SD)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>79.5 (20.2)</t>
+          <t>3.21 (0.44)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>已发表值 80 (20)</t>
+          <t>四点量表；本研究设定值，非文献报告值</t>
         </is>
       </c>
     </row>
@@ -956,7 +960,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.194, 0.193, 0.224, 0.215, 0.173</t>
+          <t>0.138, 0.258, 0.257, 0.130, 0.217</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1007,12 +1011,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.764</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>多项 logistic 探针，情节级正确率 0.901</t>
+          <t>多项 logistic 探针，情节级正确率 0.894</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1088,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>平均 |cos| 0.664，最近一对 0.890</t>
+          <t>平均 |cos| 0.711，最近一对 0.933</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1101,7 +1105,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>平均 |cos| 0.650，最近一对 0.997</t>
+          <t>平均 |cos| 0.746，最近一对 0.998</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1165,16 +1169,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9253</v>
+        <v>0.8697</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0012</v>
+        <v>0.002</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9338</v>
+        <v>0.8687</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0025</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="3">
@@ -1184,16 +1188,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9374</v>
+        <v>0.8897</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0119</v>
+        <v>0.0048</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9505</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="4">
@@ -1203,16 +1207,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9324</v>
+        <v>0.8914</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0054</v>
+        <v>0.01</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9478</v>
+        <v>0.8984</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0061</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1222,16 +1226,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9094</v>
+        <v>0.8525</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0077</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9245</v>
+        <v>0.8653</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0062</v>
+        <v>0.009299999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1241,16 +1245,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8177</v>
+        <v>0.7523</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0125</v>
+        <v>0.017</v>
       </c>
       <c r="D6" t="n">
-        <v>0.841</v>
+        <v>0.7607</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0065</v>
+        <v>0.0346</v>
       </c>
     </row>
     <row r="7">
@@ -1260,16 +1264,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9254</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0078</v>
+        <v>0.0114</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9403</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0059</v>
+        <v>0.0122</v>
       </c>
     </row>
   </sheetData>
@@ -1333,19 +1337,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8406</v>
+        <v>0.7279</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8579</v>
+        <v>0.9283</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9633</v>
+        <v>0.8962</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9869</v>
+        <v>0.8256</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9778</v>
+        <v>0.9705</v>
       </c>
     </row>
     <row r="3">
@@ -1355,19 +1359,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8598</v>
+        <v>0.8056</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.9598</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9737</v>
+        <v>0.9087</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9781</v>
+        <v>0.8175</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9728</v>
+        <v>0.9567</v>
       </c>
     </row>
     <row r="4">
@@ -1377,19 +1381,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8504</v>
+        <v>0.7725</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.971</v>
+        <v>0.9236</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9687</v>
+        <v>0.8737</v>
       </c>
       <c r="F4" t="n">
-        <v>0.955</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="5">
@@ -1399,19 +1403,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.6842</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8845</v>
+        <v>0.9155</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9391</v>
+        <v>0.8668</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9704</v>
+        <v>0.8613</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9358</v>
+        <v>0.9349</v>
       </c>
     </row>
     <row r="6">
@@ -1421,19 +1425,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6496</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7761</v>
+        <v>0.8404</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8586</v>
+        <v>0.7353</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8822</v>
+        <v>0.6859</v>
       </c>
       <c r="F6" t="n">
-        <v>0.922</v>
+        <v>0.9036999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1443,19 +1447,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.7762</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8973</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9694</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9603</v>
+        <v>0.8572</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9509</v>
+        <v>0.966</v>
       </c>
     </row>
   </sheetData>
@@ -1525,22 +1529,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.1259</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0061</v>
+        <v>0.0069</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4248</v>
+        <v>0.3393</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0279</v>
+        <v>0.0081</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5234</v>
+        <v>0.4034</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0475</v>
+        <v>0.0205</v>
       </c>
     </row>
     <row r="3">
@@ -1550,22 +1554,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1635</v>
+        <v>0.1961</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0061</v>
+        <v>0.0058</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3546</v>
+        <v>0.3105</v>
       </c>
       <c r="E3" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.0232</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.5515</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.0192</v>
       </c>
     </row>
     <row r="4">
@@ -1575,22 +1579,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2207</v>
+        <v>0.2772</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0232</v>
+        <v>0.043</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3364</v>
+        <v>0.3271</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0097</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2868</v>
+        <v>0.2726</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0317</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="5">
@@ -1600,22 +1604,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1392</v>
+        <v>0.1943</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0173</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4362</v>
+        <v>0.419</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0286</v>
+        <v>0.0153</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4806</v>
+        <v>0.4063</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0226</v>
+        <v>0.0218</v>
       </c>
     </row>
     <row r="6">
@@ -1625,22 +1629,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1536</v>
+        <v>0.1807</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0264</v>
+        <v>0.0223</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2967</v>
+        <v>0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0173</v>
+        <v>0.0381</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2212</v>
+        <v>0.2235</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0103</v>
+        <v>0.0144</v>
       </c>
     </row>
     <row r="7">
@@ -1650,22 +1654,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.172</v>
+        <v>0.2097</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008</v>
+        <v>0.0177</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4562</v>
+        <v>0.4284</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0147</v>
+        <v>0.0156</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6463</v>
+        <v>0.4828</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0166</v>
+        <v>0.0408</v>
       </c>
     </row>
     <row r="8">
@@ -1730,7 +1734,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.9041</v>
+        <v>0.7644</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1817,28 +1821,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9251</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0102</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4636</v>
+        <v>0.4365</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0053</v>
+        <v>0.0116</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6737</v>
+        <v>0.5181</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0525</v>
+        <v>0.0603</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2872</v>
+        <v>0.4211</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02</v>
+        <v>0.0133</v>
       </c>
     </row>
     <row r="3">
@@ -1848,28 +1852,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9446</v>
+        <v>0.8716</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0033</v>
+        <v>0.0126</v>
       </c>
       <c r="D3" t="n">
-        <v>0.479</v>
+        <v>0.4421</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0038</v>
+        <v>0.0381</v>
       </c>
       <c r="F3" t="n">
-        <v>0.629</v>
+        <v>0.4885</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004</v>
+        <v>0.0583</v>
       </c>
       <c r="H3" t="n">
-        <v>0.311</v>
+        <v>0.4274</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005</v>
+        <v>0.0091</v>
       </c>
     </row>
     <row r="4">
@@ -1879,28 +1883,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9067</v>
+        <v>0.8518</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0148</v>
+        <v>0.0158</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4145</v>
+        <v>0.3944</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0224</v>
+        <v>0.0091</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4512</v>
+        <v>0.3676</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0222</v>
+        <v>0.0236</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3467</v>
+        <v>0.4636</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0267</v>
+        <v>0.0216</v>
       </c>
     </row>
     <row r="5">
@@ -1910,28 +1914,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8323</v>
+        <v>0.7683</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0454</v>
+        <v>0.0414</v>
       </c>
       <c r="D5" t="n">
-        <v>0.383</v>
+        <v>0.3676</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03</v>
+        <v>0.0439</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2997</v>
+        <v>0.2859</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0277</v>
+        <v>0.0211</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5806</v>
+        <v>0.6342</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0502</v>
+        <v>0.0381</v>
       </c>
     </row>
     <row r="6">
@@ -1941,28 +1945,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9254</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0078</v>
+        <v>0.0114</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4562</v>
+        <v>0.4284</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0147</v>
+        <v>0.0156</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6463</v>
+        <v>0.4828</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0166</v>
+        <v>0.0408</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2879</v>
+        <v>0.4231</v>
       </c>
       <c r="I6" t="n">
-        <v>0.026</v>
+        <v>0.0151</v>
       </c>
     </row>
   </sheetData>
@@ -2027,14 +2031,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ERQ 认知重评 reappraisal</t>
+          <t>ERQ-CA 认知重评 reappraisal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5683</v>
+        <v>0.4601</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.00015</v>
       </c>
       <c r="E2" t="n">
         <v>63</v>
@@ -2053,14 +2057,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ERQ 表达抑制 suppression</t>
+          <t>ERQ-CA 表达抑制 suppression</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4686</v>
+        <v>0.3564</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00011</v>
+        <v>0.00415</v>
       </c>
       <c r="E3" t="n">
         <v>63</v>
@@ -2079,21 +2083,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DERS 总分 total</t>
+          <t>ERC 教师报告 teacher-reported</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.2225</v>
+        <v>0.3314</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07967</v>
+        <v>0.007979999999999999</v>
       </c>
       <c r="E4" t="n">
         <v>63</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>不显著 n.s.</t>
+          <t>p &lt; .05</t>
         </is>
       </c>
     </row>
@@ -2186,34 +2190,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8323</v>
+        <v>0.7683</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0454</v>
+        <v>0.0414</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1891</v>
+        <v>0.2208</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0245</v>
+        <v>0.0034</v>
       </c>
       <c r="F2" t="n">
-        <v>0.383</v>
+        <v>0.3676</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2997</v>
+        <v>0.2859</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0277</v>
+        <v>0.0211</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2212</v>
+        <v>0.2235</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0103</v>
+        <v>0.0144</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5806</v>
+        <v>0.6342</v>
       </c>
     </row>
     <row r="3">
@@ -2221,34 +2225,34 @@
         <v>0.005</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8309</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0456</v>
+        <v>0.044</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1923</v>
+        <v>0.2207</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0254</v>
+        <v>0.0035</v>
       </c>
       <c r="F3" t="n">
-        <v>0.379</v>
+        <v>0.3626</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3003</v>
+        <v>0.2853</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0285</v>
+        <v>0.0187</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2184</v>
+        <v>0.2226</v>
       </c>
       <c r="J3" t="n">
-        <v>0.014</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5908</v>
+        <v>0.6384</v>
       </c>
     </row>
     <row r="4">
@@ -2256,34 +2260,34 @@
         <v>0.01</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8285</v>
+        <v>0.7693</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0455</v>
+        <v>0.0437</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1959</v>
+        <v>0.2225</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0253</v>
+        <v>0.0052</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3748</v>
+        <v>0.3648</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3005</v>
+        <v>0.2851</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0271</v>
+        <v>0.0162</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2195</v>
+        <v>0.2224</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0144</v>
+        <v>0.0106</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6017</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="5">
@@ -2291,34 +2295,34 @@
         <v>0.02</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8032</v>
+        <v>0.7671</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0269</v>
+        <v>0.0443</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1974</v>
+        <v>0.2262</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0362</v>
+        <v>0.0062</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3547</v>
+        <v>0.3657</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2942</v>
+        <v>0.2861</v>
       </c>
       <c r="H5" t="n">
-        <v>0.021</v>
+        <v>0.0116</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2154</v>
+        <v>0.2199</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0172</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6191</v>
+        <v>0.6524</v>
       </c>
     </row>
     <row r="6">
@@ -2326,34 +2330,34 @@
         <v>0.05</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.7571</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0217</v>
+        <v>0.0441</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2086</v>
+        <v>0.2352</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0336</v>
+        <v>0.0059</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3469</v>
+        <v>0.3612</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2772</v>
+        <v>0.2756</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0102</v>
+        <v>0.0081</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2142</v>
+        <v>0.2159</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0121</v>
+        <v>0.0104</v>
       </c>
       <c r="K6" t="n">
-        <v>0.655</v>
+        <v>0.6834</v>
       </c>
     </row>
     <row r="7">
@@ -2361,34 +2365,34 @@
         <v>0.1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7633</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>0.056</v>
+        <v>0.045</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2438</v>
+        <v>0.243</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0335</v>
+        <v>0.011</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3802</v>
+        <v>0.3767</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2673</v>
+        <v>0.2546</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0098</v>
+        <v>0.0193</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2051</v>
+        <v>0.2127</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0092</v>
+        <v>0.0116</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7459</v>
+        <v>0.7339</v>
       </c>
     </row>
     <row r="8">
@@ -2396,34 +2400,34 @@
         <v>0.2</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7504999999999999</v>
+        <v>0.7298</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0268</v>
+        <v>0.043</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2517</v>
+        <v>0.2496</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0223</v>
+        <v>0.0149</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4146</v>
+        <v>0.3867</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2823</v>
+        <v>0.247</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0402</v>
+        <v>0.0145</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2042</v>
+        <v>0.204</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0058</v>
+        <v>0.0026</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8031</v>
+        <v>0.8035</v>
       </c>
     </row>
     <row r="9">
@@ -2503,7 +2507,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2513,7 +2517,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8729</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
